--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="236">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H2" s="9">
         <f>B208</f>
-        <v>3329000</v>
+        <v>3469000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4106,18 +4106,22 @@
     <row r="205" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <f t="shared" si="10"/>
-        <v>3329000</v>
-      </c>
-      <c r="B205" s="8"/>
+        <v>3469000</v>
+      </c>
+      <c r="B205" s="8">
+        <v>140000</v>
+      </c>
       <c r="C205" s="8"/>
-      <c r="D205" s="8"/>
+      <c r="D205" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="E205" s="1"/>
     </row>
     <row r="206" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="9"/>
       <c r="B206" s="9">
         <f>SUM(B186:B205) +B180</f>
-        <v>10665000</v>
+        <v>10805000</v>
       </c>
       <c r="C206" s="9">
         <f>SUM(C186:C205) +C180</f>
@@ -4135,7 +4139,7 @@
       <c r="A208" s="9"/>
       <c r="B208" s="12">
         <f>A205</f>
-        <v>3329000</v>
+        <v>3469000</v>
       </c>
       <c r="C208" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="238">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -727,6 +727,12 @@
   </si>
   <si>
     <t>وجه تکیه گول</t>
+  </si>
+  <si>
+    <t>1405/04/13</t>
+  </si>
+  <si>
+    <t>دنگ بوته</t>
   </si>
 </sst>
 </file>
@@ -847,7 +853,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1187,14 +1214,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="18.25" customWidth="1"/>
     <col min="4" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1224,8 +1251,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B208</f>
-        <v>3469000</v>
+        <f>B234</f>
+        <v>4111000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4146,7 +4173,7 @@
       </c>
       <c r="D208" s="14"/>
     </row>
-    <row r="209" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>86</v>
       </c>
@@ -4154,20 +4181,312 @@
         <v>85</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>10</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C210" s="2"/>
+    </row>
+    <row r="211" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A211" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="8">
+        <f>B208+B212-C212</f>
+        <v>4111000</v>
+      </c>
+      <c r="B212" s="8">
+        <v>642000</v>
+      </c>
+      <c r="C212" s="8"/>
+      <c r="D212" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="8">
+        <f>A212+B213-C213</f>
+        <v>4111000</v>
+      </c>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
+      <c r="D213" s="8"/>
+      <c r="E213" s="1"/>
+    </row>
+    <row r="214" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="8">
+        <f t="shared" ref="A214:A220" si="11">A213+B214-C214</f>
+        <v>4111000</v>
+      </c>
+      <c r="B214" s="8"/>
+      <c r="C214" s="8"/>
+      <c r="D214" s="8"/>
+      <c r="E214" s="1"/>
+    </row>
+    <row r="215" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="8">
+        <f t="shared" si="11"/>
+        <v>4111000</v>
+      </c>
+      <c r="B215" s="8"/>
+      <c r="C215" s="8"/>
+      <c r="D215" s="8"/>
+      <c r="E215" s="1"/>
+    </row>
+    <row r="216" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="8">
+        <f t="shared" si="11"/>
+        <v>4111000</v>
+      </c>
+      <c r="B216" s="8"/>
+      <c r="C216" s="8"/>
+      <c r="D216" s="8"/>
+      <c r="E216" s="1"/>
+    </row>
+    <row r="217" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="8">
+        <f t="shared" si="11"/>
+        <v>4111000</v>
+      </c>
+      <c r="B217" s="8"/>
+      <c r="C217" s="8"/>
+      <c r="D217" s="8"/>
+      <c r="E217" s="1"/>
+    </row>
+    <row r="218" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="8">
+        <f t="shared" si="11"/>
+        <v>4111000</v>
+      </c>
+      <c r="B218" s="8"/>
+      <c r="C218" s="8"/>
+      <c r="D218" s="8"/>
+      <c r="E218" s="1"/>
+    </row>
+    <row r="219" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="8">
+        <f t="shared" si="11"/>
+        <v>4111000</v>
+      </c>
+      <c r="B219" s="8"/>
+      <c r="C219" s="8"/>
+      <c r="D219" s="8"/>
+      <c r="E219" s="1"/>
+    </row>
+    <row r="220" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="8">
+        <f t="shared" si="11"/>
+        <v>4111000</v>
+      </c>
+      <c r="B220" s="8"/>
+      <c r="C220" s="8"/>
+      <c r="D220" s="8"/>
+      <c r="E220" s="1"/>
+    </row>
+    <row r="221" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="8">
+        <f>A220+B221-C221</f>
+        <v>4111000</v>
+      </c>
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
+      <c r="D221" s="8"/>
+      <c r="E221" s="1"/>
+    </row>
+    <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="8">
+        <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
+        <v>4111000</v>
+      </c>
+      <c r="B222" s="8"/>
+      <c r="C222" s="8"/>
+      <c r="D222" s="8"/>
+      <c r="E222" s="1"/>
+    </row>
+    <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="8"/>
+      <c r="E223" s="1"/>
+    </row>
+    <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="8"/>
+      <c r="E224" s="1"/>
+    </row>
+    <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B225" s="8"/>
+      <c r="C225" s="8"/>
+      <c r="D225" s="8"/>
+      <c r="E225" s="1"/>
+    </row>
+    <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B226" s="8"/>
+      <c r="C226" s="8"/>
+      <c r="D226" s="8"/>
+      <c r="E226" s="1"/>
+    </row>
+    <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="8"/>
+      <c r="E227" s="1"/>
+    </row>
+    <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="8"/>
+      <c r="E228" s="1"/>
+    </row>
+    <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
+      <c r="D229" s="8"/>
+      <c r="E229" s="1"/>
+    </row>
+    <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B230" s="8"/>
+      <c r="C230" s="8"/>
+      <c r="D230" s="8"/>
+      <c r="E230" s="1"/>
+    </row>
+    <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="8">
+        <f t="shared" si="12"/>
+        <v>4111000</v>
+      </c>
+      <c r="B231" s="8"/>
+      <c r="C231" s="8"/>
+      <c r="D231" s="8"/>
+      <c r="E231" s="1"/>
+    </row>
+    <row r="232" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="9"/>
+      <c r="B232" s="9">
+        <f>SUM(B212:B231) +B206</f>
+        <v>11447000</v>
+      </c>
+      <c r="C232" s="9">
+        <f>SUM(C212:C231) +C206</f>
+        <v>7336000</v>
+      </c>
+      <c r="D232" s="9"/>
+    </row>
+    <row r="233" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="9"/>
+      <c r="B233" s="9"/>
+      <c r="C233" s="9"/>
+      <c r="D233" s="9"/>
+    </row>
+    <row r="234" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A234" s="9"/>
+      <c r="B234" s="12">
+        <f>A231</f>
+        <v>4111000</v>
+      </c>
+      <c r="C234" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D234" s="14"/>
+    </row>
+    <row r="235" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>86</v>
+      </c>
+      <c r="D235" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="C234:D234"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C129:D129"/>
     <mergeCell ref="C156:D156"/>
@@ -4175,6 +4494,17 @@
     <mergeCell ref="C208:D208"/>
   </mergeCells>
   <conditionalFormatting sqref="B156">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B182">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4185,7 +4515,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
+  <conditionalFormatting sqref="B208">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4196,7 +4526,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B208">
+  <conditionalFormatting sqref="B234">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="239">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -733,6 +733,9 @@
   </si>
   <si>
     <t>دنگ بوته</t>
+  </si>
+  <si>
+    <t>1405/04/14</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1255,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4226,17 +4229,23 @@
     <row r="213" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f>A212+B213-C213</f>
-        <v>4111000</v>
-      </c>
-      <c r="B213" s="8"/>
+        <v>4328000</v>
+      </c>
+      <c r="B213" s="8">
+        <v>217000</v>
+      </c>
       <c r="C213" s="8"/>
-      <c r="D213" s="8"/>
-      <c r="E213" s="1"/>
+      <c r="D213" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="214" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" ref="A214:A220" si="11">A213+B214-C214</f>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4246,7 +4255,7 @@
     <row r="215" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="11"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4256,7 +4265,7 @@
     <row r="216" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="11"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -4266,7 +4275,7 @@
     <row r="217" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="11"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4276,7 +4285,7 @@
     <row r="218" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="11"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4286,7 +4295,7 @@
     <row r="219" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="11"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4296,7 +4305,7 @@
     <row r="220" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="11"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4306,7 +4315,7 @@
     <row r="221" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f>A220+B221-C221</f>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4316,7 +4325,7 @@
     <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4326,7 +4335,7 @@
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4336,7 +4345,7 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4346,7 +4355,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4356,7 +4365,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4366,7 +4375,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4376,7 +4385,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4386,7 +4395,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4396,7 +4405,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4406,7 +4415,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4417,7 +4426,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>11447000</v>
+        <v>11664000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4435,7 +4444,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4111000</v>
+        <v>4328000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="240">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -736,6 +736,9 @@
   </si>
   <si>
     <t>1405/04/14</t>
+  </si>
+  <si>
+    <t>مزه</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1258,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4245,17 +4248,21 @@
     <row r="214" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" ref="A214:A220" si="11">A213+B214-C214</f>
-        <v>4328000</v>
-      </c>
-      <c r="B214" s="8"/>
+        <v>4448000</v>
+      </c>
+      <c r="B214" s="8">
+        <v>120000</v>
+      </c>
       <c r="C214" s="8"/>
-      <c r="D214" s="8"/>
+      <c r="D214" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="E214" s="1"/>
     </row>
     <row r="215" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="11"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4265,7 +4272,7 @@
     <row r="216" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="11"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -4275,7 +4282,7 @@
     <row r="217" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="11"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4285,7 +4292,7 @@
     <row r="218" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="11"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4295,7 +4302,7 @@
     <row r="219" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="11"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4305,7 +4312,7 @@
     <row r="220" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="11"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4315,7 +4322,7 @@
     <row r="221" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f>A220+B221-C221</f>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4325,7 +4332,7 @@
     <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4335,7 +4342,7 @@
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4345,7 +4352,7 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4355,7 +4362,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4365,7 +4372,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4375,7 +4382,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4385,7 +4392,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4395,7 +4402,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4405,7 +4412,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4415,7 +4422,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4426,7 +4433,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>11664000</v>
+        <v>11784000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4444,7 +4451,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4328000</v>
+        <v>4448000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="242">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -739,6 +739,12 @@
   </si>
   <si>
     <t>مزه</t>
+  </si>
+  <si>
+    <t>1405/04/15</t>
+  </si>
+  <si>
+    <t>وجه گول کالابرگ</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1264,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4262,17 +4268,23 @@
     <row r="215" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="11"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B215" s="8"/>
-      <c r="C215" s="8"/>
-      <c r="D215" s="8"/>
-      <c r="E215" s="1"/>
+      <c r="C215" s="8">
+        <v>700000</v>
+      </c>
+      <c r="D215" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="216" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="11"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -4282,7 +4294,7 @@
     <row r="217" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="11"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4292,7 +4304,7 @@
     <row r="218" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="11"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4302,7 +4314,7 @@
     <row r="219" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="11"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4312,7 +4324,7 @@
     <row r="220" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="11"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4322,7 +4334,7 @@
     <row r="221" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f>A220+B221-C221</f>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4332,7 +4344,7 @@
     <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4342,7 +4354,7 @@
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4352,7 +4364,7 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4362,7 +4374,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4372,7 +4384,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4382,7 +4394,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4392,7 +4404,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4402,7 +4414,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4412,7 +4424,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4422,7 +4434,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4437,7 +4449,7 @@
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
-        <v>7336000</v>
+        <v>8036000</v>
       </c>
       <c r="D232" s="9"/>
     </row>
@@ -4451,7 +4463,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4448000</v>
+        <v>3748000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="243">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -745,6 +745,9 @@
   </si>
   <si>
     <t>وجه گول کالابرگ</t>
+  </si>
+  <si>
+    <t>1405/04/17</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1267,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4284,17 +4287,23 @@
     <row r="216" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="11"/>
-        <v>3748000</v>
-      </c>
-      <c r="B216" s="8"/>
+        <v>3860000</v>
+      </c>
+      <c r="B216" s="8">
+        <v>112000</v>
+      </c>
       <c r="C216" s="8"/>
-      <c r="D216" s="8"/>
-      <c r="E216" s="1"/>
+      <c r="D216" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="217" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="11"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4304,7 +4313,7 @@
     <row r="218" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="11"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4314,7 +4323,7 @@
     <row r="219" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="11"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4324,7 +4333,7 @@
     <row r="220" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="11"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4334,7 +4343,7 @@
     <row r="221" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f>A220+B221-C221</f>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4344,7 +4353,7 @@
     <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4354,7 +4363,7 @@
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4364,7 +4373,7 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4374,7 +4383,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4384,7 +4393,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4394,7 +4403,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4404,7 +4413,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4414,7 +4423,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4424,7 +4433,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4434,7 +4443,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4445,7 +4454,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>11784000</v>
+        <v>11896000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4463,7 +4472,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>3748000</v>
+        <v>3860000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="245">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -748,6 +748,12 @@
   </si>
   <si>
     <t>1405/04/17</t>
+  </si>
+  <si>
+    <t>1405/04/18</t>
+  </si>
+  <si>
+    <t>بستنی هنونه ای</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1273,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4303,17 +4309,23 @@
     <row r="217" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="11"/>
-        <v>3860000</v>
-      </c>
-      <c r="B217" s="8"/>
+        <v>3910000</v>
+      </c>
+      <c r="B217" s="8">
+        <v>50000</v>
+      </c>
       <c r="C217" s="8"/>
-      <c r="D217" s="8"/>
-      <c r="E217" s="1"/>
+      <c r="D217" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="218" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="11"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4323,7 +4335,7 @@
     <row r="219" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="11"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4333,7 +4345,7 @@
     <row r="220" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="11"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4343,7 +4355,7 @@
     <row r="221" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f>A220+B221-C221</f>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4353,7 +4365,7 @@
     <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4363,7 +4375,7 @@
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4373,7 +4385,7 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4383,7 +4395,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4393,7 +4405,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4403,7 +4415,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4413,7 +4425,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4423,7 +4435,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4433,7 +4445,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4443,7 +4455,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4454,7 +4466,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>11896000</v>
+        <v>11946000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4472,7 +4484,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>3860000</v>
+        <v>3910000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="248">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -754,6 +754,15 @@
   </si>
   <si>
     <t>بستنی هنونه ای</t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>کیک رضا</t>
+  </si>
+  <si>
+    <t>ساندویچ باغ ممد جواد</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1282,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4325,37 +4334,51 @@
     <row r="218" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="11"/>
-        <v>3910000</v>
-      </c>
-      <c r="B218" s="8"/>
+        <v>4012000</v>
+      </c>
+      <c r="B218" s="8">
+        <v>102000</v>
+      </c>
       <c r="C218" s="8"/>
-      <c r="D218" s="8"/>
-      <c r="E218" s="1"/>
+      <c r="D218" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="219" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="11"/>
-        <v>3910000</v>
-      </c>
-      <c r="B219" s="8"/>
+        <v>4097000</v>
+      </c>
+      <c r="B219" s="8">
+        <v>85000</v>
+      </c>
       <c r="C219" s="8"/>
-      <c r="D219" s="8"/>
+      <c r="D219" s="8" t="s">
+        <v>246</v>
+      </c>
       <c r="E219" s="1"/>
     </row>
     <row r="220" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="11"/>
-        <v>3910000</v>
-      </c>
-      <c r="B220" s="8"/>
+        <v>4243000</v>
+      </c>
+      <c r="B220" s="8">
+        <v>146000</v>
+      </c>
       <c r="C220" s="8"/>
-      <c r="D220" s="8"/>
+      <c r="D220" s="8" t="s">
+        <v>247</v>
+      </c>
       <c r="E220" s="1"/>
     </row>
     <row r="221" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f>A220+B221-C221</f>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4365,7 +4388,7 @@
     <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4375,7 +4398,7 @@
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4385,7 +4408,7 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4395,7 +4418,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4405,7 +4428,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4415,7 +4438,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4425,7 +4448,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4435,7 +4458,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4445,7 +4468,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4455,7 +4478,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4466,7 +4489,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>11946000</v>
+        <v>12279000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4484,7 +4507,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>3910000</v>
+        <v>4243000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="250">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -763,6 +763,12 @@
   </si>
   <si>
     <t>ساندویچ باغ ممد جواد</t>
+  </si>
+  <si>
+    <t>1405/04/22</t>
+  </si>
+  <si>
+    <t>خودکار</t>
   </si>
 </sst>
 </file>
@@ -1282,7 +1288,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4378,17 +4384,23 @@
     <row r="221" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f>A220+B221-C221</f>
-        <v>4243000</v>
-      </c>
-      <c r="B221" s="8"/>
+        <v>4318000</v>
+      </c>
+      <c r="B221" s="8">
+        <v>75000</v>
+      </c>
       <c r="C221" s="8"/>
-      <c r="D221" s="8"/>
-      <c r="E221" s="1"/>
+      <c r="D221" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4398,7 +4410,7 @@
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4408,7 +4420,7 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4418,7 +4430,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4428,7 +4440,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4438,7 +4450,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4448,7 +4460,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4458,7 +4470,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4468,7 +4480,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4478,7 +4490,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4489,7 +4501,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12279000</v>
+        <v>12354000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4507,7 +4519,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4243000</v>
+        <v>4318000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="251">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -769,6 +769,9 @@
   </si>
   <si>
     <t>خودکار</t>
+  </si>
+  <si>
+    <t>1405/04/24</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1291,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4400,17 +4403,23 @@
     <row r="222" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" ref="A222:A231" si="12">A221+B222-C222</f>
-        <v>4318000</v>
-      </c>
-      <c r="B222" s="8"/>
+        <v>4364000</v>
+      </c>
+      <c r="B222" s="8">
+        <v>46000</v>
+      </c>
       <c r="C222" s="8"/>
-      <c r="D222" s="8"/>
-      <c r="E222" s="1"/>
+      <c r="D222" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4420,7 +4429,7 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4430,7 +4439,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4440,7 +4449,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4450,7 +4459,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4460,7 +4469,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4470,7 +4479,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4480,7 +4489,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4490,7 +4499,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4501,7 +4510,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12354000</v>
+        <v>12400000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4519,7 +4528,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4318000</v>
+        <v>4364000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="253">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -772,6 +772,12 @@
   </si>
   <si>
     <t>1405/04/24</t>
+  </si>
+  <si>
+    <t>1405/04/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الباقی قهوه </t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1297,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4419,17 +4425,23 @@
     <row r="223" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
-      </c>
-      <c r="B223" s="8"/>
+        <v>4424000</v>
+      </c>
+      <c r="B223" s="8">
+        <v>60000</v>
+      </c>
       <c r="C223" s="8"/>
-      <c r="D223" s="8"/>
-      <c r="E223" s="1"/>
+      <c r="D223" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4439,7 +4451,7 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4449,7 +4461,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4459,7 +4471,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4469,7 +4481,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4479,7 +4491,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4489,7 +4501,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4499,7 +4511,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4510,7 +4522,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12400000</v>
+        <v>12460000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4528,7 +4540,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4364000</v>
+        <v>4424000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="254">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -778,6 +778,9 @@
   </si>
   <si>
     <t xml:space="preserve">الباقی قهوه </t>
+  </si>
+  <si>
+    <t>1405/04/27</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1300,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4441,17 +4444,23 @@
     <row r="224" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="12"/>
-        <v>4424000</v>
-      </c>
-      <c r="B224" s="8"/>
+        <v>4494000</v>
+      </c>
+      <c r="B224" s="8">
+        <v>70000</v>
+      </c>
       <c r="C224" s="8"/>
-      <c r="D224" s="8"/>
-      <c r="E224" s="1"/>
+      <c r="D224" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4461,7 +4470,7 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4471,7 +4480,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4481,7 +4490,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4491,7 +4500,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4501,7 +4510,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4511,7 +4520,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4522,7 +4531,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12460000</v>
+        <v>12530000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4540,7 +4549,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4424000</v>
+        <v>4494000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="254">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4494000</v>
+        <v>4656000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4460,17 +4460,21 @@
     <row r="225" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="12"/>
-        <v>4494000</v>
-      </c>
-      <c r="B225" s="8"/>
+        <v>4656000</v>
+      </c>
+      <c r="B225" s="8">
+        <v>162000</v>
+      </c>
       <c r="C225" s="8"/>
-      <c r="D225" s="8"/>
+      <c r="D225" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="E225" s="1"/>
     </row>
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4494000</v>
+        <v>4656000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4480,7 +4484,7 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4494000</v>
+        <v>4656000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4490,7 +4494,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4494000</v>
+        <v>4656000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4500,7 +4504,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4494000</v>
+        <v>4656000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4510,7 +4514,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4494000</v>
+        <v>4656000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4520,7 +4524,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4494000</v>
+        <v>4656000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4531,7 +4535,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12530000</v>
+        <v>12692000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4549,7 +4553,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4494000</v>
+        <v>4656000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="256">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -781,6 +781,12 @@
   </si>
   <si>
     <t>1405/04/27</t>
+  </si>
+  <si>
+    <t>1405/04/29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وچه </t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1306,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4656000</v>
+        <v>4526000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4474,17 +4480,23 @@
     <row r="226" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="12"/>
-        <v>4656000</v>
+        <v>4526000</v>
       </c>
       <c r="B226" s="8"/>
-      <c r="C226" s="8"/>
-      <c r="D226" s="8"/>
-      <c r="E226" s="1"/>
+      <c r="C226" s="8">
+        <v>130000</v>
+      </c>
+      <c r="D226" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4656000</v>
+        <v>4526000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4494,7 +4506,7 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4656000</v>
+        <v>4526000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4504,7 +4516,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4656000</v>
+        <v>4526000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4514,7 +4526,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4656000</v>
+        <v>4526000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4524,7 +4536,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4656000</v>
+        <v>4526000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4539,7 +4551,7 @@
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
-        <v>8036000</v>
+        <v>8166000</v>
       </c>
       <c r="D232" s="9"/>
     </row>
@@ -4553,7 +4565,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4656000</v>
+        <v>4526000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="257">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -787,6 +787,9 @@
   </si>
   <si>
     <t xml:space="preserve">وچه </t>
+  </si>
+  <si>
+    <t>1405/05/01</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1309,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4526000</v>
+        <v>4606000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4496,17 +4499,23 @@
     <row r="227" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="12"/>
-        <v>4526000</v>
-      </c>
-      <c r="B227" s="8"/>
+        <v>4606000</v>
+      </c>
+      <c r="B227" s="8">
+        <v>80000</v>
+      </c>
       <c r="C227" s="8"/>
-      <c r="D227" s="8"/>
-      <c r="E227" s="1"/>
+      <c r="D227" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4526000</v>
+        <v>4606000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4516,7 +4525,7 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4526000</v>
+        <v>4606000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4526,7 +4535,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4526000</v>
+        <v>4606000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4536,7 +4545,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4526000</v>
+        <v>4606000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4547,7 +4556,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12692000</v>
+        <v>12772000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4565,7 +4574,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4526000</v>
+        <v>4606000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="258">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -790,6 +790,9 @@
   </si>
   <si>
     <t>1405/05/01</t>
+  </si>
+  <si>
+    <t>1405/05/09</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1312,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4606000</v>
+        <v>4768000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4515,17 +4518,23 @@
     <row r="228" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="12"/>
-        <v>4606000</v>
-      </c>
-      <c r="B228" s="8"/>
+        <v>4768000</v>
+      </c>
+      <c r="B228" s="8">
+        <v>162000</v>
+      </c>
       <c r="C228" s="8"/>
-      <c r="D228" s="8"/>
-      <c r="E228" s="1"/>
+      <c r="D228" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4606000</v>
+        <v>4768000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4535,7 +4544,7 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4606000</v>
+        <v>4768000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4545,7 +4554,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4606000</v>
+        <v>4768000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4556,7 +4565,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12772000</v>
+        <v>12934000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4574,7 +4583,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4606000</v>
+        <v>4768000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="260">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -793,6 +793,12 @@
   </si>
   <si>
     <t>1405/05/09</t>
+  </si>
+  <si>
+    <t>1405/05/11</t>
+  </si>
+  <si>
+    <t>تاینی های بای</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1318,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4768000</v>
+        <v>4828000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4534,17 +4540,23 @@
     <row r="229" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="12"/>
-        <v>4768000</v>
-      </c>
-      <c r="B229" s="8"/>
+        <v>4828000</v>
+      </c>
+      <c r="B229" s="8">
+        <v>60000</v>
+      </c>
       <c r="C229" s="8"/>
-      <c r="D229" s="8"/>
-      <c r="E229" s="1"/>
+      <c r="D229" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4768000</v>
+        <v>4828000</v>
       </c>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
@@ -4554,7 +4566,7 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4768000</v>
+        <v>4828000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4565,7 +4577,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12934000</v>
+        <v>12994000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4583,7 +4595,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4768000</v>
+        <v>4828000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="262">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -799,6 +799,12 @@
   </si>
   <si>
     <t>تاینی های بای</t>
+  </si>
+  <si>
+    <t>1405/05/13</t>
+  </si>
+  <si>
+    <t>گول بازی مزه باغ دامو</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1324,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>4828000</v>
+        <v>5087000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4556,17 +4562,23 @@
     <row r="230" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <f t="shared" si="12"/>
-        <v>4828000</v>
-      </c>
-      <c r="B230" s="8"/>
+        <v>5087000</v>
+      </c>
+      <c r="B230" s="8">
+        <v>259000</v>
+      </c>
       <c r="C230" s="8"/>
-      <c r="D230" s="8"/>
-      <c r="E230" s="1"/>
+      <c r="D230" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>4828000</v>
+        <v>5087000</v>
       </c>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -4577,7 +4589,7 @@
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>12994000</v>
+        <v>13253000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4595,7 +4607,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>4828000</v>
+        <v>5087000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="263">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -805,6 +805,9 @@
   </si>
   <si>
     <t>گول بازی مزه باغ دامو</t>
+  </si>
+  <si>
+    <t>1405/05/20</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1327,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>5087000</v>
+        <v>5137000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4578,18 +4581,24 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>5087000</v>
-      </c>
-      <c r="B231" s="8"/>
+        <v>5137000</v>
+      </c>
+      <c r="B231" s="8">
+        <v>50000</v>
+      </c>
       <c r="C231" s="8"/>
-      <c r="D231" s="8"/>
-      <c r="E231" s="1"/>
+      <c r="D231" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="232" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>13253000</v>
+        <v>13303000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4607,7 +4616,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>5087000</v>
+        <v>5137000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="262">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -805,9 +805,6 @@
   </si>
   <si>
     <t>گول بازی مزه باغ دامو</t>
-  </si>
-  <si>
-    <t>1405/05/20</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1324,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>5137000</v>
+        <v>5087000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4581,24 +4578,18 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>5137000</v>
-      </c>
-      <c r="B231" s="8">
-        <v>50000</v>
-      </c>
+        <v>5087000</v>
+      </c>
+      <c r="B231" s="8"/>
       <c r="C231" s="8"/>
-      <c r="D231" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E231" s="1" t="s">
-        <v>262</v>
-      </c>
+      <c r="D231" s="8"/>
+      <c r="E231" s="1"/>
     </row>
     <row r="232" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>13303000</v>
+        <v>13253000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4616,7 +4607,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>5137000</v>
+        <v>5087000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="263">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -805,6 +805,9 @@
   </si>
   <si>
     <t>گول بازی مزه باغ دامو</t>
+  </si>
+  <si>
+    <t>1405/05/23</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1327,7 @@
       </c>
       <c r="H2" s="9">
         <f>B234</f>
-        <v>5087000</v>
+        <v>5187000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4578,18 +4581,24 @@
     <row r="231" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <f t="shared" si="12"/>
-        <v>5087000</v>
-      </c>
-      <c r="B231" s="8"/>
+        <v>5187000</v>
+      </c>
+      <c r="B231" s="8">
+        <v>100000</v>
+      </c>
       <c r="C231" s="8"/>
-      <c r="D231" s="8"/>
-      <c r="E231" s="1"/>
+      <c r="D231" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="232" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="9"/>
       <c r="B232" s="9">
         <f>SUM(B212:B231) +B206</f>
-        <v>13253000</v>
+        <v>13353000</v>
       </c>
       <c r="C232" s="9">
         <f>SUM(C212:C231) +C206</f>
@@ -4607,7 +4616,7 @@
       <c r="A234" s="9"/>
       <c r="B234" s="12">
         <f>A231</f>
-        <v>5087000</v>
+        <v>5187000</v>
       </c>
       <c r="C234" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="263">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -928,7 +928,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1326,8 +1347,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B234</f>
-        <v>5187000</v>
+        <f>B261</f>
+        <v>5379000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4632,41 +4653,289 @@
       </c>
     </row>
     <row r="236" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>10</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C237" s="2"/>
+    </row>
+    <row r="238" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A238" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D238" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="8">
+        <f>B234+B239-C239</f>
+        <v>5349000</v>
+      </c>
+      <c r="B239" s="8">
+        <v>162000</v>
+      </c>
+      <c r="C239" s="8"/>
+      <c r="D239" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="8">
+        <f>A239+B240-C240</f>
+        <v>5379000</v>
+      </c>
+      <c r="B240" s="8">
+        <v>30000</v>
+      </c>
+      <c r="C240" s="8"/>
+      <c r="D240" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E240" s="1"/>
+    </row>
+    <row r="241" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="8">
+        <f t="shared" ref="A241:A247" si="13">A240+B241-C241</f>
+        <v>5379000</v>
+      </c>
+      <c r="B241" s="8"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="8"/>
+      <c r="E241" s="1"/>
+    </row>
+    <row r="242" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="8">
+        <f t="shared" si="13"/>
+        <v>5379000</v>
+      </c>
+      <c r="B242" s="8"/>
+      <c r="C242" s="8"/>
+      <c r="D242" s="8"/>
+      <c r="E242" s="1"/>
+    </row>
+    <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="8">
+        <f t="shared" si="13"/>
+        <v>5379000</v>
+      </c>
+      <c r="B243" s="8"/>
+      <c r="C243" s="8"/>
+      <c r="D243" s="8"/>
+      <c r="E243" s="1"/>
+    </row>
+    <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="8">
+        <f>A243+B244-C244</f>
+        <v>5379000</v>
+      </c>
+      <c r="B244" s="8"/>
+      <c r="C244" s="8"/>
+      <c r="D244" s="8"/>
+      <c r="E244" s="1"/>
+    </row>
+    <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="8">
+        <f t="shared" si="13"/>
+        <v>5379000</v>
+      </c>
+      <c r="B245" s="8"/>
+      <c r="C245" s="8"/>
+      <c r="D245" s="8"/>
+      <c r="E245" s="1"/>
+    </row>
+    <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="8">
+        <f t="shared" si="13"/>
+        <v>5379000</v>
+      </c>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
+      <c r="D246" s="8"/>
+      <c r="E246" s="1"/>
+    </row>
+    <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="8">
+        <f t="shared" si="13"/>
+        <v>5379000</v>
+      </c>
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="8"/>
+      <c r="E247" s="1"/>
+    </row>
+    <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="8">
+        <f>A247+B248-C248</f>
+        <v>5379000</v>
+      </c>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="8"/>
+      <c r="E248" s="1"/>
+    </row>
+    <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="8">
+        <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
+        <v>5379000</v>
+      </c>
+      <c r="B249" s="8"/>
+      <c r="C249" s="8"/>
+      <c r="D249" s="8"/>
+      <c r="E249" s="1"/>
+    </row>
+    <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B250" s="8"/>
+      <c r="C250" s="8"/>
+      <c r="D250" s="8"/>
+      <c r="E250" s="1"/>
+    </row>
+    <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B251" s="8"/>
+      <c r="C251" s="8"/>
+      <c r="D251" s="8"/>
+      <c r="E251" s="1"/>
+    </row>
+    <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B252" s="8"/>
+      <c r="C252" s="8"/>
+      <c r="D252" s="8"/>
+      <c r="E252" s="1"/>
+    </row>
+    <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B253" s="8"/>
+      <c r="C253" s="8"/>
+      <c r="D253" s="8"/>
+      <c r="E253" s="1"/>
+    </row>
+    <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B254" s="8"/>
+      <c r="C254" s="8"/>
+      <c r="D254" s="8"/>
+      <c r="E254" s="1"/>
+    </row>
+    <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B255" s="8"/>
+      <c r="C255" s="8"/>
+      <c r="D255" s="8"/>
+      <c r="E255" s="1"/>
+    </row>
+    <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B256" s="8"/>
+      <c r="C256" s="8"/>
+      <c r="D256" s="8"/>
+      <c r="E256" s="1"/>
+    </row>
+    <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B257" s="8"/>
+      <c r="C257" s="8"/>
+      <c r="D257" s="8"/>
+      <c r="E257" s="1"/>
+    </row>
+    <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="8">
+        <f t="shared" si="14"/>
+        <v>5379000</v>
+      </c>
+      <c r="B258" s="8"/>
+      <c r="C258" s="8"/>
+      <c r="D258" s="8"/>
+      <c r="E258" s="1"/>
+    </row>
+    <row r="259" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="9"/>
+      <c r="B259" s="9">
+        <f>SUM(B239:B258) +B233</f>
+        <v>192000</v>
+      </c>
+      <c r="C259" s="9">
+        <f>SUM(C239:C258) +C233</f>
+        <v>0</v>
+      </c>
+      <c r="D259" s="9"/>
+    </row>
+    <row r="260" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="9"/>
+      <c r="B260" s="9"/>
+      <c r="C260" s="9"/>
+      <c r="D260" s="9"/>
+    </row>
+    <row r="261" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A261" s="9"/>
+      <c r="B261" s="12">
+        <f>A258</f>
+        <v>5379000</v>
+      </c>
+      <c r="C261" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D261" s="14"/>
+    </row>
+    <row r="262" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>86</v>
+      </c>
+      <c r="D262" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C261:D261"/>
     <mergeCell ref="C234:D234"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C129:D129"/>
@@ -4675,6 +4944,17 @@
     <mergeCell ref="C208:D208"/>
   </mergeCells>
   <conditionalFormatting sqref="B156">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B182">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4685,7 +4965,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
+  <conditionalFormatting sqref="B208">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4696,7 +4976,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B208">
+  <conditionalFormatting sqref="B234">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4707,7 +4987,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B234">
+  <conditionalFormatting sqref="B261">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="264">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -808,6 +808,9 @@
   </si>
   <si>
     <t>1405/05/23</t>
+  </si>
+  <si>
+    <t>1405/05/26</t>
   </si>
 </sst>
 </file>
@@ -4692,7 +4695,7 @@
         <v>188</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4715,9 +4715,11 @@
     <row r="241" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" ref="A241:A247" si="13">A240+B241-C241</f>
-        <v>5379000</v>
-      </c>
-      <c r="B241" s="8"/>
+        <v>5379005</v>
+      </c>
+      <c r="B241" s="8">
+        <v>5</v>
+      </c>
       <c r="C241" s="8"/>
       <c r="D241" s="8"/>
       <c r="E241" s="1"/>
@@ -4725,7 +4727,7 @@
     <row r="242" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4735,7 +4737,7 @@
     <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4745,7 +4747,7 @@
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4755,7 +4757,7 @@
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4765,7 +4767,7 @@
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4775,7 +4777,7 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4785,7 +4787,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4795,7 +4797,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4805,7 +4807,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4815,7 +4817,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4825,7 +4827,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4835,7 +4837,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4845,7 +4847,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4855,7 +4857,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4865,7 +4867,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4875,7 +4877,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4885,7 +4887,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4896,7 +4898,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>192000</v>
+        <v>192005</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4914,7 +4916,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5379000</v>
+        <v>5379005</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4715,10 +4715,10 @@
     <row r="241" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" ref="A241:A247" si="13">A240+B241-C241</f>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B241" s="8">
-        <v>5</v>
+        <v>50000</v>
       </c>
       <c r="C241" s="8"/>
       <c r="D241" s="8"/>
@@ -4727,7 +4727,7 @@
     <row r="242" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="13"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4737,7 +4737,7 @@
     <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="13"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4747,7 +4747,7 @@
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4757,7 +4757,7 @@
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4767,7 +4767,7 @@
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4777,7 +4777,7 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4787,7 +4787,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4797,7 +4797,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4807,7 +4807,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4817,7 +4817,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4827,7 +4827,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4837,7 +4837,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4847,7 +4847,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4857,7 +4857,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4867,7 +4867,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4877,7 +4877,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4887,7 +4887,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4898,7 +4898,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>192005</v>
+        <v>242000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4916,7 +4916,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5379005</v>
+        <v>5429000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4715,11 +4715,9 @@
     <row r="241" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" ref="A241:A247" si="13">A240+B241-C241</f>
-        <v>5429000</v>
-      </c>
-      <c r="B241" s="8">
-        <v>50000</v>
-      </c>
+        <v>5379000</v>
+      </c>
+      <c r="B241" s="8"/>
       <c r="C241" s="8"/>
       <c r="D241" s="8"/>
       <c r="E241" s="1"/>
@@ -4727,7 +4725,7 @@
     <row r="242" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="13"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4737,7 +4735,7 @@
     <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="13"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4747,7 +4745,7 @@
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4757,7 +4755,7 @@
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4767,7 +4765,7 @@
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4777,7 +4775,7 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4787,7 +4785,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4797,7 +4795,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4807,7 +4805,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4817,7 +4815,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4827,7 +4825,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4837,7 +4835,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4847,7 +4845,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4857,7 +4855,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4867,7 +4865,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4877,7 +4875,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4887,7 +4885,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4898,7 +4896,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>242000</v>
+        <v>192000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4916,7 +4914,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5429000</v>
+        <v>5379000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="265">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -811,6 +811,9 @@
   </si>
   <si>
     <t>1405/05/26</t>
+  </si>
+  <si>
+    <t>1405/06/01</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1354,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4715,17 +4718,23 @@
     <row r="241" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <f t="shared" ref="A241:A247" si="13">A240+B241-C241</f>
-        <v>5379000</v>
-      </c>
-      <c r="B241" s="8"/>
+        <v>5450000</v>
+      </c>
+      <c r="B241" s="8">
+        <v>71000</v>
+      </c>
       <c r="C241" s="8"/>
-      <c r="D241" s="8"/>
-      <c r="E241" s="1"/>
+      <c r="D241" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
@@ -4735,7 +4744,7 @@
     <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4745,7 +4754,7 @@
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4755,7 +4764,7 @@
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4765,7 +4774,7 @@
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4775,7 +4784,7 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4785,7 +4794,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4795,7 +4804,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4805,7 +4814,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4815,7 +4824,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4825,7 +4834,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4835,7 +4844,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4845,7 +4854,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4855,7 +4864,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4865,7 +4874,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4875,7 +4884,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4885,7 +4894,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4896,7 +4905,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>192000</v>
+        <v>263000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4914,7 +4923,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5379000</v>
+        <v>5450000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="266">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -814,6 +814,9 @@
   </si>
   <si>
     <t>1405/06/01</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1357,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4734,17 +4737,23 @@
     <row r="242" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <f t="shared" si="13"/>
-        <v>5450000</v>
-      </c>
-      <c r="B242" s="8"/>
+        <v>5639000</v>
+      </c>
+      <c r="B242" s="8">
+        <v>189000</v>
+      </c>
       <c r="C242" s="8"/>
-      <c r="D242" s="8"/>
-      <c r="E242" s="1"/>
+      <c r="D242" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="13"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
@@ -4754,7 +4763,7 @@
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4764,7 +4773,7 @@
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4774,7 +4783,7 @@
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4784,7 +4793,7 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4794,7 +4803,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4804,7 +4813,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4814,7 +4823,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4824,7 +4833,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4834,7 +4843,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4844,7 +4853,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4854,7 +4863,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4864,7 +4873,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4874,7 +4883,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4884,7 +4893,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4894,7 +4903,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4905,7 +4914,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>263000</v>
+        <v>452000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4923,7 +4932,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5450000</v>
+        <v>5639000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="268">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -817,6 +817,12 @@
   </si>
   <si>
     <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>دنگ سوسیس خونه یاسین</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1363,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4753,17 +4759,23 @@
     <row r="243" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <f t="shared" si="13"/>
-        <v>5639000</v>
-      </c>
-      <c r="B243" s="8"/>
+        <v>5755000</v>
+      </c>
+      <c r="B243" s="8">
+        <v>116000</v>
+      </c>
       <c r="C243" s="8"/>
-      <c r="D243" s="8"/>
-      <c r="E243" s="1"/>
+      <c r="D243" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
@@ -4773,7 +4785,7 @@
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4783,7 +4795,7 @@
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4793,7 +4805,7 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4803,7 +4815,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4813,7 +4825,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4823,7 +4835,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4833,7 +4845,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4843,7 +4855,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4853,7 +4865,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4863,7 +4875,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4873,7 +4885,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4883,7 +4895,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4893,7 +4905,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4903,7 +4915,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4914,7 +4926,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>452000</v>
+        <v>568000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4932,7 +4944,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5639000</v>
+        <v>5755000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="270">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -823,6 +823,12 @@
   </si>
   <si>
     <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/09</t>
+  </si>
+  <si>
+    <t>مزه پل دوآب</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1369,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4775,17 +4781,23 @@
     <row r="244" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <f>A243+B244-C244</f>
-        <v>5755000</v>
-      </c>
-      <c r="B244" s="8"/>
+        <v>5925000</v>
+      </c>
+      <c r="B244" s="8">
+        <v>170000</v>
+      </c>
       <c r="C244" s="8"/>
-      <c r="D244" s="8"/>
-      <c r="E244" s="1"/>
+      <c r="D244" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
@@ -4795,7 +4807,7 @@
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
@@ -4805,7 +4817,7 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4815,7 +4827,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4825,7 +4837,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4835,7 +4847,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4845,7 +4857,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4855,7 +4867,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4865,7 +4877,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4875,7 +4887,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4885,7 +4897,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4895,7 +4907,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4905,7 +4917,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4915,7 +4927,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4926,7 +4938,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>568000</v>
+        <v>738000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4944,7 +4956,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5755000</v>
+        <v>5925000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="272">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -829,6 +829,12 @@
   </si>
   <si>
     <t>مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>دنگ باغ ممدجواد</t>
   </si>
 </sst>
 </file>
@@ -1369,7 +1375,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4797,27 +4803,37 @@
     <row r="245" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <f t="shared" si="13"/>
-        <v>5925000</v>
-      </c>
-      <c r="B245" s="8"/>
+        <v>6080000</v>
+      </c>
+      <c r="B245" s="8">
+        <v>155000</v>
+      </c>
       <c r="C245" s="8"/>
-      <c r="D245" s="8"/>
-      <c r="E245" s="1"/>
+      <c r="D245" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="246" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <f t="shared" si="13"/>
-        <v>5925000</v>
-      </c>
-      <c r="B246" s="8"/>
+        <v>6280000</v>
+      </c>
+      <c r="B246" s="8">
+        <v>200000</v>
+      </c>
       <c r="C246" s="8"/>
-      <c r="D246" s="8"/>
+      <c r="D246" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="E246" s="1"/>
     </row>
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4827,7 +4843,7 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4837,7 +4853,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4847,7 +4863,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4857,7 +4873,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4867,7 +4883,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4877,7 +4893,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4887,7 +4903,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4897,7 +4913,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4907,7 +4923,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4917,7 +4933,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4927,7 +4943,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4938,7 +4954,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>738000</v>
+        <v>1093000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4956,7 +4972,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>5925000</v>
+        <v>6280000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="274">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -835,6 +835,12 @@
   </si>
   <si>
     <t>دنگ باغ ممدجواد</t>
+  </si>
+  <si>
+    <t>1405/06/16</t>
+  </si>
+  <si>
+    <t>های بای کیک</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1381,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4833,17 +4839,23 @@
     <row r="247" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <f t="shared" si="13"/>
-        <v>6280000</v>
-      </c>
-      <c r="B247" s="8"/>
+        <v>6335000</v>
+      </c>
+      <c r="B247" s="8">
+        <v>55000</v>
+      </c>
       <c r="C247" s="8"/>
-      <c r="D247" s="8"/>
-      <c r="E247" s="1"/>
+      <c r="D247" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
@@ -4853,7 +4865,7 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4863,7 +4875,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4873,7 +4885,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4883,7 +4895,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4893,7 +4905,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4903,7 +4915,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4913,7 +4925,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4923,7 +4935,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4933,7 +4945,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4943,7 +4955,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4954,7 +4966,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>1093000</v>
+        <v>1148000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4972,7 +4984,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6280000</v>
+        <v>6335000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="275">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -841,6 +841,9 @@
   </si>
   <si>
     <t>های بای کیک</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1384,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4855,17 +4858,23 @@
     <row r="248" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <f>A247+B248-C248</f>
-        <v>6335000</v>
-      </c>
-      <c r="B248" s="8"/>
+        <v>6522000</v>
+      </c>
+      <c r="B248" s="8">
+        <v>187000</v>
+      </c>
       <c r="C248" s="8"/>
-      <c r="D248" s="8"/>
-      <c r="E248" s="1"/>
+      <c r="D248" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
@@ -4875,7 +4884,7 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4885,7 +4894,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4895,7 +4904,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4905,7 +4914,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4915,7 +4924,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4925,7 +4934,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4935,7 +4944,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4945,7 +4954,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4955,7 +4964,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4966,7 +4975,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>1148000</v>
+        <v>1335000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4984,7 +4993,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6335000</v>
+        <v>6522000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>
